--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.85054647687557</v>
+        <v>7.28821380249228</v>
       </c>
       <c r="D2" t="n">
-        <v>41.41827727110768</v>
+        <v>6.730470056554998</v>
       </c>
       <c r="E2" t="n">
-        <v>18.65244708091124</v>
+        <v>3.031022650648076</v>
       </c>
       <c r="F2" t="n">
-        <v>8.54836036098707</v>
+        <v>1.389108558660399</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.24860694586469</v>
+        <v>8.165398628703011</v>
       </c>
       <c r="D3" t="n">
-        <v>64.64788635187051</v>
+        <v>10.50528153217896</v>
       </c>
       <c r="E3" t="n">
-        <v>18.65244708091124</v>
+        <v>3.031022650648076</v>
       </c>
       <c r="F3" t="n">
-        <v>8.54836036098707</v>
+        <v>1.389108558660399</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.216918780219698</v>
+        <v>1.335249301785701</v>
       </c>
       <c r="D4" t="n">
-        <v>54.67898379025233</v>
+        <v>8.885334865916004</v>
       </c>
       <c r="E4" t="n">
-        <v>18.65244708091124</v>
+        <v>3.031022650648076</v>
       </c>
       <c r="F4" t="n">
-        <v>8.54836036098707</v>
+        <v>1.389108558660399</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.96891000598511</v>
+        <v>2.107447875972579</v>
       </c>
       <c r="D5" t="n">
-        <v>58.83331808352706</v>
+        <v>9.560414188573148</v>
       </c>
       <c r="E5" t="n">
-        <v>18.65244708091124</v>
+        <v>3.031022650648076</v>
       </c>
       <c r="F5" t="n">
-        <v>8.54836036098707</v>
+        <v>1.389108558660399</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
